--- a/201025_Results_Cali/mapas/Geo_Cali/Comunas.xlsx
+++ b/201025_Results_Cali/mapas/Geo_Cali/Comunas.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Natura/201025_Results_Cali/mapas/Geo_Cali/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{90AC51B1-A7F6-4240-B42A-7AC06C0B2AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E09FC11-641A-4590-8AC3-9702AB62AA83}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{90AC51B1-A7F6-4240-B42A-7AC06C0B2AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1606E59-495F-4C9E-A8C7-D0D26E418751}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0B915248-85A3-8B4D-BC75-7086951E584C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="3" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="4" r:id="rId1"/>
     <sheet name="Resumen" sheetId="2" r:id="rId2"/>
     <sheet name="Poblacion" sheetId="1" r:id="rId3"/>
   </sheets>
@@ -300,7 +300,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -330,17 +330,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -680,528 +674,331 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E41ADAD-410E-4C37-9D04-CCEAD2A660F9}">
-  <dimension ref="A1:S23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CD94AEA-7660-4339-AD2F-D0048FAF0C07}">
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.296875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" cm="1">
-        <f t="array" ref="A2:A23">_xlfn.SEQUENCE(22)</f>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
-        <f>Poblacion!$D6</f>
+      <c r="B2">
         <v>60799</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2">
         <v>0.46799999999999997</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2">
         <v>0.53200000000000003</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
-        <f>Poblacion!H6</f>
+      <c r="B3">
         <v>118956</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3">
         <v>0.46200000000000002</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3">
         <v>0.53799999999999992</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
-        <f>Poblacion!L6</f>
+      <c r="B4">
         <v>33652</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4">
         <v>0.48799999999999999</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4">
         <v>0.51200000000000001</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="7">
-        <f>Poblacion!P6</f>
+      <c r="B5">
         <v>56189</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5">
         <v>0.46200000000000002</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5">
         <v>0.53799999999999992</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7">
-        <f>Poblacion!D17</f>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
         <v>114776</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6">
         <v>0.44299999999999995</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6">
         <v>0.55700000000000005</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="7">
-        <f>Poblacion!H17</f>
+      <c r="B7">
         <v>154154</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7">
         <v>0.46100000000000002</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7">
         <v>0.53900000000000003</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="7">
-        <f>Poblacion!L17</f>
+      <c r="B8">
         <v>71049</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8">
         <v>0.45899999999999996</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8">
         <v>0.54100000000000004</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="7">
-        <f>Poblacion!P17</f>
+      <c r="B9">
         <v>100226</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9">
         <v>0.45299999999999996</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9">
         <v>0.54700000000000004</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="7">
-        <f>Poblacion!D28</f>
+      <c r="B10">
         <v>37165</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10">
         <v>0.47600000000000003</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10">
         <v>0.52400000000000002</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="7">
-        <f>Poblacion!H28</f>
+      <c r="B11">
         <v>104729</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11">
         <v>0.44900000000000001</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11">
         <v>0.55100000000000005</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="7">
-        <f>Poblacion!L28</f>
+      <c r="B12">
         <v>111204</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12">
         <v>0.45600000000000002</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12">
         <v>0.54400000000000004</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="7">
-        <f>Poblacion!P28</f>
+      <c r="B13">
         <v>69956</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13">
         <v>0.46</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13">
         <v>0.54</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="7">
-        <f>Poblacion!D39</f>
+      <c r="B14">
         <v>145047</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14">
         <v>0.46100000000000002</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14">
         <v>0.53900000000000003</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="7">
-        <f>Poblacion!H39</f>
+      <c r="B15">
         <v>157639</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15">
         <v>0.46</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15">
         <v>0.54</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="5">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="7">
-        <f>Poblacion!L39</f>
+      <c r="B16">
         <v>126766</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16">
         <v>0.45299999999999996</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16">
         <v>0.54700000000000004</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="7">
-        <f>Poblacion!P39</f>
+      <c r="B17">
         <v>99041</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17">
         <v>0.46</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17">
         <v>0.54</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="5">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="7">
-        <f>Poblacion!D50</f>
+      <c r="B18">
         <v>168998</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18">
         <v>0.43099999999999999</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18">
         <v>0.56899999999999995</v>
       </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="7">
-        <f>Poblacion!H50</f>
+      <c r="B19">
         <v>115529</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19">
         <v>0.46500000000000002</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19">
         <v>0.53500000000000003</v>
       </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="5">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="7">
-        <f>Poblacion!L50</f>
+      <c r="B20">
         <v>111310</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20">
         <v>0.46600000000000003</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20">
         <v>0.53400000000000003</v>
       </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="7">
-        <f>Poblacion!P50</f>
+      <c r="B21">
         <v>58827</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21">
         <v>0.47</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21">
         <v>0.53</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="7">
-        <f>Poblacion!D61</f>
+      <c r="B22">
         <v>132544</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22">
         <v>0.45799999999999996</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22">
         <v>0.54200000000000004</v>
       </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="7">
-        <f>Poblacion!H61</f>
+      <c r="B23">
         <v>26104</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23">
         <v>0.498</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23">
         <v>0.502</v>
       </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2052,45 +1849,45 @@
       <c r="P1" s="4"/>
     </row>
     <row r="2" spans="2:16" ht="58.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="F4" s="14" t="s">
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="F4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="J4" s="14" t="s">
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="J4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="N4" s="14" t="s">
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="N4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
@@ -2419,26 +2216,26 @@
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="F15" s="14" t="s">
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="F15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="J15" s="14" t="s">
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="J15" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="N15" s="14" t="s">
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="N15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
@@ -2767,26 +2564,26 @@
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="F26" s="14" t="s">
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="F26" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="J26" s="14" t="s">
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="J26" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="N26" s="14" t="s">
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="N26" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
@@ -3115,26 +2912,26 @@
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="F37" s="14" t="s">
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="F37" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="J37" s="14" t="s">
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="J37" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="N37" s="14" t="s">
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="N37" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="11"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
@@ -3463,26 +3260,26 @@
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="F48" s="14" t="s">
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="F48" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="J48" s="14" t="s">
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="J48" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="N48" s="14" t="s">
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="N48" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="O48" s="14"/>
-      <c r="P48" s="14"/>
+      <c r="O48" s="11"/>
+      <c r="P48" s="11"/>
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
@@ -3811,16 +3608,16 @@
       </c>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="F59" s="14" t="s">
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="F59" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
@@ -3996,16 +3793,11 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="F59:H59"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="N4:P4"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="J15:L15"/>
@@ -4014,11 +3806,16 @@
     <mergeCell ref="F26:H26"/>
     <mergeCell ref="J26:L26"/>
     <mergeCell ref="N26:P26"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="J48:L48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="F59:H59"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="J37:L37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
